--- a/site/exports/seu-humanities.xlsx
+++ b/site/exports/seu-humanities.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,16 +443,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22.4" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -569,10 +569,118 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>人文学院/社会学系</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>原本人硕士生导师资格是指导他人，不是本人求学导师；副教授及2020-10至2024-03讲师职业行分别保留，当前人事未独立核验。；日本东北大学博士（文学）、硕士（文学）明确来源获授；同期国际安全学项目不能累加第二博士，原学习期末不作为授位年月。；2018美国Northeastern University政治学系访问学者与日本东北大学不是同一机构。；社会学系具名目录及原人文学院社会学系职业单位完整保留；复用人文学院展示节点不独立认证行政层级。目录具名链接未点击，raw href与目标未核。；研究方向：环境社会学、组织社会学、灾害社会学、数字社会学。两作品保原章节/译者类型，个人页“图书章节”分类不作为整书或完整译者名单认证。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；有限公开职业资料，非完整履历或实时人事认证；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：组织社会学（专业必修课）；角色未披露；教学／课程开设时间：时间未披露；原本科生课程栏目列示组织社会学（专业必修课）；栏目层级及必修/选修性质保留，原必要片段未明确主讲动词，不补角色或当前课表。；来源ID：seu-yemaoxin-profile；https://rwxy.seu.edu.cn/ymx/main.htm | 社区社会工作（专业选修课）；角色未披露；教学／课程开设时间：时间未披露；原研究生课程栏目列示社区社会工作（专业选修课）；栏目层级及必修/选修性质保留，原必要片段未明确主讲动词，不补角色或当前课表。；来源ID：seu-yemaoxin-profile；https://rwxy.seu.edu.cn/ymx/main.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>人文学院（官网域及教育史上下文）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>原页列副教授、副院长，起任日期未披露；人文学院仅官网域名及教育史上下文关联，任职行未明列学院，不能据此认定副院长所属学院。；三项本人教育资格及学校、时间原样保留；授位日期未单列，不把学习区间末年当授位年。；所留资料未披露本人导师，不由任职或合作者推定师承。；论文和专著原列名作者保留，未核出版者元数据或全文，不从署名顺序推具体贡献。；官网列博士生导师、硕士生导师，仅为本人指导他人的资格，不另造岗位或本人求学导师。；原2018年入选东南大学“至善青年学者”计划；不扩写计划性质或推当前资格。；研究方向原列老年社会学，聚焦老年移民生活质量、老龄化社会与文化变迁、数字化技术与养老服务模式。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,16 +692,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="25.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="43.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -601,7 +709,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
@@ -979,13 +1087,673 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>博士（文学）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>日本东北大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>行为科学</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>原日本东北大学行为科学博士毕业，明确博士（文学）学位；2017-04至2020-03为学习区间，不填授位日或法律实体认证。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>日本东北大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>国际安全学项目（Inter-Graduate School Doctoral Degree Program on Science for Global Safety）</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>同为2017-04至2020-03的日本东北大学国际安全学项目博士标签，完整英文项目名保留；不能累计成第二个获授博士，独立授位未知。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>硕士（文学）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>日本东北大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>行为科学</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>原日本东北大学行为科学硕士毕业，明确硕士（文学）学位；2015-04至2017-03学习区间不转授位年月。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>nondegree_training</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>美国Northeastern University</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>原2018-09至2018-11美国Northeastern University政治学系访问学者，为非学位；与日本东北大学是不同机构，不因中文译名相似合并。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>原人文学院社会学系副教授，2024年4月-至今；完整原单位保留，至今措辞（如原列有）不认证当前人事。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>原人文学院社会学系讲师，2020年10月-2024年3月；完整原单位保留，至今措辞（如原列有）不认证当前人事。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>法学学士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>东南大学人文学院社会学系</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>原2003至2007，东南大学人文学院社会学系，法学学士；学习年月按原列，授位日期未单独核实。 官网具名本人履历以具体学位资格列举，按来源报告学位；不表示已核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>哲学硕士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>东南大学人文学院哲学与科学系</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>原2007至2010，东南大学人文学院哲学与科学系，哲学硕士；学习年月按原列，授位日期未单独核实。 官网具名本人履历以具体学位资格列举，按来源报告学位；不表示已核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>社会学博士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>新西兰奥克兰大学社会学系</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>社会学</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>原2010至2014，新西兰奥克兰大学社会学系，社会学博士；学习年月按原列，授位日期未单独核实。原列教育部公派。 官网具名本人履历以具体学位资格列举，按来源报告学位；不表示已核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>副教授；副院长</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>原页列副教授、副院长，起任年月未给；任职原行未明列学院，机构仅记东南大学，人文学院来自官网域名和教育史上下文，不认定该副院长职务所属学院。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1088,19 +1856,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="46.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="43.4" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1279,8 +2047,200 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>中国应急与灾害社会工作的发展与未来</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>图书章节（原列）；book_chapter_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026叶茂鑫著章节《中国应急与灾害社会工作的发展与未来》，载《社会工作的职业化与专精化》，任文启、杨爱兵主编，北京：北京大学出版社；章节作者不变全书主编，未核出版者或全文。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>不平等的形成：日本社会的差异、分层和公正</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>译著（原栏目）；translated_work_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>原置“图书章节”栏目，2013《不平等的形成：日本社会的差异、分层和公正》，[日本]佐藤嘉伦、木村敏明著，叶茂鑫等译，北京：社会科学文献出版社。原著作者与译者分离，保留“等”，不推完整译者名单或整书/章节范围。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>教育代际流动如何影响老年人数字融入——资源补偿与陪伴缺失的双重逻辑</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文；journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>官网书目，未核出版者元数据或全文；official_publication_list_only</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>原署名张晶晶、张望；东南大学学报（哲学与社会科学版）2026年28卷4期116–128页，保留列名作者角色，不据作者顺序推贡献或通讯作者。 原书目附CSSCI标签，仅保留当时来源表述，未独立核现行收录。</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>流动时代的老年生活质量</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>书籍；book</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>官网书目，未核出版者元数据或全文；official_publication_list_only</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>原列张晶晶，2022年，东南大学出版社，ISBN 978-7-5766-0053-7；保留列名作者，不自动推独著，未核全文。 原括注东南大学高水平专著出版计划，仅为该书来源标签，不另作获奖或独立出版认证。</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1288,6 +2248,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1299,13 +2265,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="33.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="53.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -1381,10 +2347,124 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>seu-yemaoxin-profile</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/ymx/main.htm</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>official_public_body_read</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>叶茂鑫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>seu-humanities-directory</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/8787/list.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>official_public_body_read</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张晶晶</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>profile-1-392</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/zjj/list.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/seu-humanities.xlsx
+++ b/site/exports/seu-humanities.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -675,12 +675,66 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>人文学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Partial biography, current employment/directory unknown.；Year-degree labels not forced into award or graduation years.；Own mentors unknown, coauthors not mentorship.；Official bibliography only; source journal spelling retained, publisher metadata unverified.；Liu source only explicitly names School of Humanities, exact tourism departmental affiliation not asserted.；Original necessary raw professional lines saved immediately privately.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,11 +746,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="25.2" customWidth="1" min="2" max="2"/>
+    <col width="36.4" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="43.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -774,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1737,8 +1791,285 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>degree_qualification_label</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>河南大学历史文化学院</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Year beside degree label; no explicit conferral verb, not asserted graduation/award date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（year_label_as_source）：2013</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>degree_qualification_label</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>英国萨里大学商学院</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Year beside degree label; no explicit conferral verb, not asserted graduation/award date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（year_label_as_source）：2014</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>degree_qualification_label</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>香港理工大学酒店及旅游业管理学院</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Year beside degree label; no explicit conferral verb, not asserted graduation/award date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（year_label_as_source）：2020</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>东南大学人文学院</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：副教授；来源institution_as_source：东南大学人文学院；来源记载（year_label_as_source）：2025</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>美国天普大学美—亚旅游研究中心</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：访问学者；来源institution_as_source：美国天普大学美—亚旅游研究中心；来源记载（year_label_as_source）：2019</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S15"/>
+  <autoFilter ref="A1:S20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1754,6 +2085,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1856,11 +2192,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="46.2" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
@@ -2239,8 +2575,112 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Phygital heuristics in tourists’ decision-making in motion</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Liu, X., Wang, D.*, &amp; Li, X.；来源person_contribution_role_as_source：listed author; no inferred corresponding status；来源书目信息（文章编号）：10963480251319979</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Effect of intergenerational relationships in daily life on travel behaviors of adult children and parents: A comparative study of the two generations’ perspectives</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Liu, X., Liu, C.*, Qi, Z., &amp; Sun, H.；来源person_contribution_role_as_source：listed author; no inferred corresponding status；来源书目信息（卷）：60；来源书目信息（页码）：405-415</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2254,6 +2694,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2265,14 +2709,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="33.59999999999999" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="53.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2458,13 +2902,51 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>刘雪蕊</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-seu-liuxuerui-tourism-s001-370cf62b5939</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://rwxy.seu.edu.cn/lxr/list.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:07:18Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
